--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty IT ETF.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty IT ETF.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="63">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty IT ETF</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -118,13 +118,10 @@
     <t>INE356A01018</t>
   </si>
   <si>
-    <t>L&amp;T Technology Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE010V01017</t>
-  </si>
-  <si>
-    <t>It - Services</t>
+    <t>Oracle Financial Services Software Ltd.</t>
+  </si>
+  <si>
+    <t>INE881D01027</t>
   </si>
   <si>
     <t>Unlisted</t>
@@ -178,6 +175,12 @@
     <t>Total Net Assets</t>
   </si>
   <si>
+    <t>Details of the Equity shares have been lent under Securities Lending and Borrowing as follows:-</t>
+  </si>
+  <si>
+    <t>Name of the Instrument</t>
+  </si>
+  <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
@@ -190,7 +193,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -200,9 +203,6 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - NIFTY IT TRI</t>
   </si>
 </sst>
 </file>
@@ -214,7 +214,7 @@
     <numFmt numFmtId="178" formatCode="##0.00%"/>
     <numFmt numFmtId="179" formatCode="##0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -230,6 +230,18 @@
       <sz val="8.25"/>
       <name val="Microsoft Sans Serif"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -290,7 +302,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -376,6 +388,20 @@
         <color auto="1"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -402,44 +428,44 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
@@ -466,17 +492,35 @@
       <alignment horizontal="right"/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -573,13 +617,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -597,7 +641,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="12077700"/>
+          <a:off x="666750" y="12649200"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -612,13 +656,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -636,7 +680,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="14935200"/>
+          <a:off x="666750" y="15506700"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -970,19 +1014,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J75"/>
+  <dimension ref="B1:J77"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="21" width="53.57142857142857" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="21" width="16.285714285714285" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="21" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="21" width="19.714285714285715" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="21" width="10.857142857142858" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="21" width="38.714285714285715" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="21" width="11.714285714285714" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="21" width="29.714285714285715" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="21" width="26.714285714285715" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="26" width="10.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="26" width="53.57142857142857" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="26" width="16.285714285714285" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="26" width="9.714285714285714" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="26" width="19.714285714285715" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="26" width="10.857142857142858" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="26" width="38.714285714285715" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="26" width="11.714285714285714" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="26" width="29.714285714285715" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="26" width="26.714285714285715" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1">
@@ -1070,10 +1114,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>49418.280000000006</v>
+        <v>47115.20</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9939670445414</v>
+        <v>0.9958477995938999</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1107,10 +1151,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>49418.280000000006</v>
+        <v>47115.20</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9939670445414</v>
+        <v>0.9958477995938999</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1133,13 +1177,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>744731</v>
+        <v>821319</v>
       </c>
       <c r="G8" s="15">
-        <v>13999.45</v>
+        <v>12834.75</v>
       </c>
       <c r="H8" s="16">
-        <v>0.2815758043726</v>
+        <v>0.2712809782372</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1162,13 +1206,13 @@
         <v>17</v>
       </c>
       <c r="F9" s="14">
-        <v>280447</v>
+        <v>302185</v>
       </c>
       <c r="G9" s="15">
-        <v>11533.10</v>
+        <v>10465.88</v>
       </c>
       <c r="H9" s="16">
-        <v>0.231969249464</v>
+        <v>0.221211489473</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1191,13 +1235,13 @@
         <v>17</v>
       </c>
       <c r="F10" s="14">
-        <v>290502</v>
+        <v>313981</v>
       </c>
       <c r="G10" s="15">
-        <v>5012.47</v>
+        <v>5138.61</v>
       </c>
       <c r="H10" s="16">
-        <v>0.1008175515569</v>
+        <v>0.1086119439474</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1220,13 +1264,13 @@
         <v>17</v>
       </c>
       <c r="F11" s="14">
-        <v>288524</v>
+        <v>308977</v>
       </c>
       <c r="G11" s="15">
-        <v>4831.19</v>
+        <v>4862.99</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0971714038999</v>
+        <v>0.1027863171746</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1249,13 +1293,13 @@
         <v>17</v>
       </c>
       <c r="F12" s="14">
-        <v>1287013</v>
+        <v>1383312</v>
       </c>
       <c r="G12" s="15">
-        <v>4014.19</v>
+        <v>3453.72</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0807387988924</v>
+        <v>0.0729993603426</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1278,13 +1322,13 @@
         <v>17</v>
       </c>
       <c r="F13" s="14">
-        <v>47901</v>
+        <v>51831</v>
       </c>
       <c r="G13" s="15">
-        <v>2889.68</v>
+        <v>2922.23</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0581211383575</v>
+        <v>0.0617655515716</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1307,13 +1351,13 @@
         <v>17</v>
       </c>
       <c r="F14" s="14">
-        <v>30248</v>
+        <v>32405</v>
       </c>
       <c r="G14" s="15">
-        <v>2499.65</v>
+        <v>2770.79</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0502763293843</v>
+        <v>0.0585646484497</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1336,13 +1380,13 @@
         <v>17</v>
       </c>
       <c r="F15" s="14">
-        <v>42036</v>
+        <v>44951</v>
       </c>
       <c r="G15" s="15">
-        <v>2486.07</v>
+        <v>2278.52</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0500031901236</v>
+        <v>0.0481598110234</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1365,13 +1409,13 @@
         <v>17</v>
       </c>
       <c r="F16" s="14">
-        <v>51376</v>
+        <v>55327</v>
       </c>
       <c r="G16" s="15">
-        <v>1473.44</v>
+        <v>1415.71</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0296358109207</v>
+        <v>0.0299230755332</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1391,16 +1435,16 @@
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F17" s="14">
-        <v>12461</v>
+        <v>11486</v>
       </c>
       <c r="G17" s="15">
-        <v>679.04</v>
+        <v>972</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0136577675695</v>
+        <v>0.0205446238412</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1419,7 +1463,7 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>13</v>
@@ -1434,10 +1478,10 @@
         <v>13</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I19" s="9" t="s">
         <v>13</v>
@@ -1456,7 +1500,7 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>13</v>
@@ -1471,10 +1515,10 @@
         <v>13</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I21" s="9" t="s">
         <v>13</v>
@@ -1508,10 +1552,10 @@
         <v>13</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I23" s="9" t="s">
         <v>13</v>
@@ -1530,7 +1574,7 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>13</v>
@@ -1545,10 +1589,10 @@
         <v>13</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I25" s="9" t="s">
         <v>13</v>
@@ -1567,7 +1611,7 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>13</v>
@@ -1582,10 +1626,10 @@
         <v>13</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I27" s="9" t="s">
         <v>13</v>
@@ -1604,7 +1648,7 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>13</v>
@@ -1619,10 +1663,10 @@
         <v>13</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I29" s="9" t="s">
         <v>13</v>
@@ -1641,7 +1685,7 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>13</v>
@@ -1656,10 +1700,10 @@
         <v>13</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I31" s="9" t="s">
         <v>13</v>
@@ -1678,7 +1722,7 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>13</v>
@@ -1693,10 +1737,10 @@
         <v>13</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I33" s="9" t="s">
         <v>13</v>
@@ -1715,7 +1759,7 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>13</v>
@@ -1730,10 +1774,10 @@
         <v>13</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I35" s="9" t="s">
         <v>13</v>
@@ -1752,7 +1796,7 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>13</v>
@@ -1767,10 +1811,10 @@
         <v>13</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I37" s="9" t="s">
         <v>13</v>
@@ -1789,7 +1833,7 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
       <c r="B39" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>13</v>
@@ -1804,10 +1848,10 @@
         <v>13</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I39" s="9" t="s">
         <v>13</v>
@@ -1826,7 +1870,7 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>13</v>
@@ -1841,10 +1885,10 @@
         <v>13</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I41" s="9" t="s">
         <v>13</v>
@@ -1863,7 +1907,7 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
       <c r="B43" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>13</v>
@@ -1878,10 +1922,10 @@
         <v>13</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I43" s="9" t="s">
         <v>13</v>
@@ -1900,25 +1944,25 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="9">
+        <v>0.54</v>
+      </c>
+      <c r="H45" s="16" t="s">
         <v>50</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G45" s="9">
-        <v>0.60</v>
-      </c>
-      <c r="H45" s="16" t="s">
-        <v>51</v>
       </c>
       <c r="I45" s="9" t="s">
         <v>13</v>
@@ -1937,7 +1981,7 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
       <c r="B47" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C47" s="18" t="s">
         <v>13</v>
@@ -1952,10 +1996,10 @@
         <v>13</v>
       </c>
       <c r="G47" s="18">
-        <v>299.34785409998585</v>
+        <v>195.90744170000107</v>
       </c>
       <c r="H47" s="19">
-        <v>0.0060208874495372875</v>
+        <v>0.004140786725750968</v>
       </c>
       <c r="I47" s="18" t="s">
         <v>13</v>
@@ -1966,126 +2010,143 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C48" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" s="18">
+        <v>47311.6474417</v>
+      </c>
+      <c r="H48" s="19">
+        <v>0.9999999999995509</v>
+      </c>
+      <c r="I48" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J48" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" ht="15" customHeight="1">
+      <c r="B50" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C48" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F48" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48" s="18">
-        <v>49718.2278541</v>
-      </c>
-      <c r="H48" s="19">
-        <v>0.9999999999994372</v>
-      </c>
-      <c r="I48" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J48" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="51" spans="2:9" ht="15" customHeight="1">
-      <c r="B51" s="13" t="s">
+      <c r="C50" s="22"/>
+    </row>
+    <row r="51" spans="2:3" ht="15" customHeight="1">
+      <c r="B51" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="21"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="21"/>
-    </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="B52" s="13" t="s">
+      <c r="C51" s="24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" ht="15" customHeight="1">
+      <c r="B52" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="25">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" ht="15" customHeight="1">
+      <c r="B54" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C52" s="21"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="21"/>
-      <c r="G52" s="21"/>
-      <c r="H52" s="21"/>
-    </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
-      <c r="B53" s="13" t="s">
+      <c r="C54" s="26"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="26"/>
+      <c r="H54" s="26"/>
+      <c r="I54" s="26"/>
+    </row>
+    <row r="55" spans="2:8" ht="15" customHeight="1">
+      <c r="B55" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C53" s="21"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="21"/>
-      <c r="G53" s="21"/>
-      <c r="H53" s="21"/>
-    </row>
-    <row r="54" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B54" s="22" t="s">
+      <c r="C55" s="26"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="26"/>
+      <c r="G55" s="26"/>
+      <c r="H55" s="26"/>
+    </row>
+    <row r="56" spans="2:8" ht="15" customHeight="1">
+      <c r="B56" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C54" s="21"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="21"/>
-      <c r="G54" s="21"/>
-      <c r="H54" s="21"/>
-    </row>
-    <row r="55" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B55" s="22" t="s">
+      <c r="C56" s="26"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
+      <c r="H56" s="26"/>
+    </row>
+    <row r="57" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B57" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="C55" s="21"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="21"/>
-      <c r="G55" s="21"/>
-      <c r="H55" s="21"/>
-    </row>
-    <row r="56" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B56" s="22" t="s">
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
+      <c r="H57" s="26"/>
+    </row>
+    <row r="58" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B58" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="C56" s="21"/>
-      <c r="D56" s="21"/>
-      <c r="E56" s="21"/>
-      <c r="F56" s="21"/>
-      <c r="G56" s="21"/>
-      <c r="H56" s="21"/>
-    </row>
-    <row r="59" ht="15">
-      <c r="B59" s="21" t="s">
+      <c r="C58" s="26"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="26"/>
+      <c r="H58" s="26"/>
+    </row>
+    <row r="59" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B59" s="27" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="74" ht="15">
-      <c r="B74" s="21" t="s">
+      <c r="C59" s="26"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="26"/>
+      <c r="F59" s="26"/>
+      <c r="G59" s="26"/>
+      <c r="H59" s="26"/>
+    </row>
+    <row r="62" ht="15">
+      <c r="B62" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="75" ht="15">
-      <c r="B75" s="21" t="s">
+    <row r="77" ht="15">
+      <c r="B77" s="26" t="s">
         <v>62</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B53:H53"/>
-    <mergeCell ref="B54:H54"/>
-    <mergeCell ref="B55:H55"/>
     <mergeCell ref="B56:H56"/>
+    <mergeCell ref="B57:H57"/>
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B59:H59"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B51:I51"/>
-    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B54:I54"/>
+    <mergeCell ref="B55:H55"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
